--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_arica_y_parinacota.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>31.04270907230345</v>
+      </c>
+      <c r="C2">
         <v>28.46748322210852</v>
-      </c>
-      <c r="C2">
-        <v>31.04270907230345</v>
       </c>
       <c r="D2">
         <v>3.512779799316352</v>
       </c>
       <c r="E2">
-        <v>17.84681142479307</v>
+        <v>19.46126991998552</v>
       </c>
       <c r="F2">
         <v>62.69191865522141</v>
       </c>
       <c r="G2">
-        <v>19.46126991998552</v>
+        <v>17.84681142479307</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>34.15977961432507</v>
+      </c>
+      <c r="C3">
         <v>53.99449035812672</v>
-      </c>
-      <c r="C3">
-        <v>34.15977961432507</v>
       </c>
       <c r="D3">
         <v>1.852040816326531</v>
       </c>
       <c r="E3">
-        <v>28.69692532942899</v>
+        <v>18.15519765739385</v>
       </c>
       <c r="F3">
         <v>53.14787701317717</v>
       </c>
       <c r="G3">
-        <v>18.15519765739385</v>
+        <v>28.69692532942899</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>33.63057324840764</v>
+      </c>
+      <c r="C4">
         <v>37.70700636942675</v>
-      </c>
-      <c r="C4">
-        <v>33.63057324840764</v>
       </c>
       <c r="D4">
         <v>2.652027027027027</v>
       </c>
       <c r="E4">
-        <v>22.00743494423792</v>
+        <v>19.62825278810409</v>
       </c>
       <c r="F4">
         <v>58.36431226765799</v>
       </c>
       <c r="G4">
-        <v>19.62825278810409</v>
+        <v>22.00743494423792</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>42.15686274509804</v>
+      </c>
+      <c r="C5">
         <v>43.13725490196079</v>
-      </c>
-      <c r="C5">
-        <v>42.15686274509804</v>
       </c>
       <c r="D5">
         <v>2.318181818181818</v>
       </c>
       <c r="E5">
+        <v>22.75132275132275</v>
+      </c>
+      <c r="F5">
+        <v>53.96825396825396</v>
+      </c>
+      <c r="G5">
         <v>23.28042328042328</v>
-      </c>
-      <c r="F5">
-        <v>53.96825396825397</v>
-      </c>
-      <c r="G5">
-        <v>22.75132275132275</v>
       </c>
     </row>
   </sheetData>
